--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.10</t>
+          <t>0.61 ± 0.10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.41 ± 0.13</t>
+          <t>0.39 ± 0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80 ± 0.28</t>
+          <t>0.78 ± 0.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.27 ± 0.34</t>
+          <t>0.28 ± 0.37</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.47 ± 0.21</t>
+          <t>0.52 ± 0.21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,12 +528,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.85 ± 0.14</t>
+          <t>0.90 ± 0.11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F4" t="n">
